--- a/data-manipulation-scripts/sheets-cleanup/sheets/CAPA CHUVA- 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CAPA CHUVA- 29_01.xlsx
@@ -367,7 +367,9 @@
       <c r="C2" s="2">
         <v>3.0</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="2">
+        <v>175.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -379,7 +381,9 @@
       <c r="C3" s="2">
         <v>2.0</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="2">
+        <v>175.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -391,7 +395,9 @@
       <c r="C4" s="2">
         <v>2.0</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="2">
+        <v>175.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -403,7 +409,9 @@
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>175.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -415,7 +423,9 @@
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>175.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -427,7 +437,9 @@
       <c r="C7" s="2">
         <v>3.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>175.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
